--- a/lib/reimbursements/templates/EUSA_international_payment_template.xlsx
+++ b/lib/reimbursements/templates/EUSA_international_payment_template.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27624"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Finance\Departmental\08-PROCESSES &amp; PROCEDURES\FORMS ETC\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22125" windowHeight="10065"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520"/>
   </bookViews>
   <sheets>
     <sheet name="FORM" sheetId="1" r:id="rId5"/>
@@ -31,12 +31,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="46" count="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="42" count="42">
   <si>
     <t>INTERNATIONAL PAYMENT REQUEST</t>
   </si>
@@ -47,30 +50,9 @@
     <t>PAYEE:</t>
   </si>
   <si>
-    <t>pretix</t>
-  </si>
-  <si>
     <t>DESCRIPTION OF EXPENSE</t>
   </si>
   <si>
-    <t>invoice R202402861 (pretix fees)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">AMOUNT  </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <b val="1"/>
-        <color theme="1"/>
-        <sz val="11"/>
-      </rPr>
-      <t>€</t>
-    </r>
-  </si>
-  <si>
     <t>DATE REQUIRED</t>
   </si>
   <si>
@@ -80,19 +62,10 @@
     <t>COST CENTRE</t>
   </si>
   <si>
-    <t>BED</t>
-  </si>
-  <si>
     <t>BIC/SWIFT CODE</t>
   </si>
   <si>
-    <t>GENODEM1GLS</t>
-  </si>
-  <si>
     <t>IBAN NUMBER</t>
-  </si>
-  <si>
-    <t>DE34 4306 0967 1147 5589 00</t>
   </si>
   <si>
     <r>
@@ -226,6 +199,12 @@
   <si>
     <t>DIRECTOR / CEO</t>
   </si>
+  <si>
+    <t xml:space="preserve">AMOUNT  </t>
+  </si>
+  <si>
+    <t>PAYMENT CURRENCY</t>
+  </si>
 </sst>
 </file>
 
@@ -237,7 +216,7 @@
     <numFmt numFmtId="166" formatCode="00\-00\-00"/>
     <numFmt numFmtId="167" formatCode="00000000"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -283,13 +262,6 @@
       <color theme="1"/>
       <sz val="12"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="10">
@@ -489,7 +461,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -638,6 +610,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -730,9 +705,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -770,7 +745,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -876,7 +851,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1018,7 +993,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1029,7 +1004,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="D2:E27"/>
+  <dimension ref="D2:E28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3.5703125" customWidth="1"/>
@@ -1061,213 +1036,205 @@
       <c r="B8" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="53" t="str">
-        <v/>
-      </c>
+      <c r="C8" s="53"/>
       <c r="D8" s="53"/>
       <c r="E8" s="53"/>
     </row>
     <row r="9" spans="2:5" customFormat="false" ht="49.15" customHeight="1">
       <c r="B9" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="52" t="str">
-        <v/>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="C9" s="52"/>
       <c r="D9" s="53"/>
       <c r="E9" s="53"/>
     </row>
     <row r="10" spans="2:5" customFormat="false" ht="30" customHeight="1">
       <c r="B10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="10"/>
+      <c r="D10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="32"/>
+    </row>
+    <row r="11" spans="2:5" customFormat="false" ht="30" customHeight="1">
+      <c r="B11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="10"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="54"/>
+    </row>
+    <row r="12" spans="2:5" customFormat="false" ht="32.25" customHeight="1">
+      <c r="B12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="10" t="str">
-        <v/>
-      </c>
-      <c r="D10" s="3" t="s">
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="2:5" customFormat="false" ht="29.25" customHeight="1">
+      <c r="B13" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="32" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="11" spans="2:5" customFormat="false" ht="32.25" customHeight="1">
-      <c r="B11" s="3" t="s">
+      <c r="C13" s="11"/>
+      <c r="D13" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="2" t="str">
-        <v/>
-      </c>
-      <c r="D11" s="3" t="s">
+      <c r="E13" s="12"/>
+    </row>
+    <row r="14" spans="2:4" customFormat="false" ht="13.5" customHeight="1">
+      <c r="B14" s="1"/>
+      <c r="D14" s="1"/>
+    </row>
+    <row r="15" spans="2:5" customFormat="false" ht="24.75" customHeight="1">
+      <c r="B15" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="12" spans="2:5" customFormat="false" ht="29.25" customHeight="1">
-      <c r="B12" s="3" t="s">
+      <c r="C15" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="11" t="str">
-        <v/>
-      </c>
-      <c r="D12" s="13" t="s">
+      <c r="E15" s="28" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" customFormat="false" ht="32.85" customHeight="1">
+      <c r="B16" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E12" s="12" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="2:4" customFormat="false" ht="13.5" customHeight="1">
-      <c r="B13" s="1"/>
-      <c r="D13" s="1"/>
-    </row>
-    <row r="14" spans="2:5" customFormat="false" ht="24.75" customHeight="1">
-      <c r="B14" s="3" t="s">
+      <c r="C16" s="27"/>
+      <c r="D16" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="27"/>
+    </row>
+    <row r="17" spans="2:5" customFormat="false" ht="18.4" customHeight="1">
+      <c r="B17" s="21"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="24"/>
+    </row>
+    <row r="18" spans="2:5" customFormat="false" ht="15.75">
+      <c r="B18" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="28" t="s">
+      <c r="C18" s="47"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="48"/>
+    </row>
+    <row r="19" spans="2:5" customFormat="false" ht="30.75" customHeight="1">
+      <c r="B19" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E14" s="28" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5" customFormat="false" ht="32.85" customHeight="1">
-      <c r="B15" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="27"/>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="27"/>
-    </row>
-    <row r="16" spans="2:5" customFormat="false" ht="18.4" customHeight="1">
-      <c r="B16" s="21"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="24"/>
-    </row>
-    <row r="17" spans="2:5" customFormat="false" ht="15.75">
-      <c r="B17" s="46" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="47"/>
-      <c r="D17" s="47"/>
-      <c r="E17" s="48"/>
-    </row>
-    <row r="18" spans="2:5" customFormat="false" ht="30.75" customHeight="1">
-      <c r="B18" s="37" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" s="36" t="str">
+      <c r="C19" s="36" t="str">
         <f>IF(C10&lt;=999.99, LISTS!A9,LISTS!A12)</f>
         <v>FINANCE TEAM CO-ORDINATOR or FINANCE ANALYST</v>
       </c>
-      <c r="D18" s="40" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" s="42" t="str">
+      <c r="D19" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" s="42" t="str">
         <f>IF(C10&gt;=10000,LISTS!A13,LISTS!A12)</f>
         <v>N/A</v>
       </c>
     </row>
-    <row r="19" spans="2:5" customFormat="false" ht="34.5" customHeight="1">
-      <c r="B19" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="35" t="str">
+    <row r="20" spans="2:5" customFormat="false" ht="34.5" customHeight="1">
+      <c r="B20" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="35" t="str">
         <f>IF(C10&gt;=1000,LISTS!A11,LISTS!A12)</f>
         <v>N/A</v>
       </c>
-      <c r="D19" s="39"/>
-      <c r="E19" s="41"/>
-    </row>
-    <row r="20" spans="2:5" customFormat="false" ht="30" customHeight="1">
-      <c r="B20" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="14"/>
-      <c r="D20" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="E20" s="14"/>
-    </row>
-    <row r="21" spans="2:5" customFormat="false" ht="54.75" customHeight="1">
-      <c r="B21" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E21" s="2"/>
-    </row>
-    <row r="22" spans="2:5" customFormat="false" ht="31.15" customHeight="1">
+      <c r="D20" s="39"/>
+      <c r="E20" s="41"/>
+    </row>
+    <row r="21" spans="2:5" customFormat="false" ht="30" customHeight="1">
+      <c r="B21" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="14"/>
+      <c r="D21" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="14"/>
+    </row>
+    <row r="22" spans="2:5" customFormat="false" ht="54.75" customHeight="1">
       <c r="B22" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" s="29" t="s">
-        <v>28</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C22" s="2"/>
       <c r="D22" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E22" s="28"/>
-    </row>
-    <row r="23" spans="2:5" customFormat="false" ht="33" customHeight="1">
+        <v>20</v>
+      </c>
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23" spans="2:5" customFormat="false" ht="31.15" customHeight="1">
       <c r="B23" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C23" s="9"/>
+        <v>21</v>
+      </c>
+      <c r="C23" s="29" t="s">
+        <v>22</v>
+      </c>
       <c r="D23" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E23" s="9"/>
-    </row>
-    <row r="24" spans="2:5" customFormat="false" ht="15" customHeight="1">
-      <c r="B24" s="21"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="25"/>
+        <v>21</v>
+      </c>
+      <c r="E23" s="28"/>
+    </row>
+    <row r="24" spans="2:5" customFormat="false" ht="33" customHeight="1">
+      <c r="B24" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="9"/>
+      <c r="D24" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="9"/>
     </row>
     <row r="25" spans="2:5" customFormat="false" ht="15" customHeight="1">
-      <c r="B25" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="C25" s="44"/>
-      <c r="D25" s="44"/>
-      <c r="E25" s="45"/>
-    </row>
-    <row r="26" spans="2:5" customFormat="false" ht="33" customHeight="1">
-      <c r="B26" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="C26" s="9"/>
-      <c r="D26" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="E26" s="9"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="25"/>
+    </row>
+    <row r="26" spans="2:5" customFormat="false" ht="15" customHeight="1">
+      <c r="B26" s="43" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="44"/>
+      <c r="D26" s="44"/>
+      <c r="E26" s="45"/>
     </row>
     <row r="27" spans="2:5" customFormat="false" ht="33" customHeight="1">
       <c r="B27" s="20" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="20" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E27" s="9"/>
+    </row>
+    <row r="28" spans="2:5" customFormat="false" ht="33" customHeight="1">
+      <c r="B28" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C28" s="9"/>
+      <c r="D28" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E28" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B18:E18"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="C9:E9"/>
     <mergeCell ref="C8:E8"/>
@@ -1285,25 +1252,25 @@
           <x14:formula1>
             <xm:f>LISTS!$A$3:$A$4</xm:f>
           </x14:formula1>
-          <xm:sqref>C14</xm:sqref>
+          <xm:sqref>C15</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000001000000}">
           <x14:formula1>
             <xm:f>LISTS!$C$3:$C$4</xm:f>
           </x14:formula1>
-          <xm:sqref>E14 C16</xm:sqref>
+          <xm:sqref>E15 C17</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000002000000}">
           <x14:formula1>
             <xm:f>LISTS!$G$3:$G$6</xm:f>
           </x14:formula1>
-          <xm:sqref>E22</xm:sqref>
+          <xm:sqref>E23</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000003000000}">
           <x14:formula1>
             <xm:f>LISTS!$E$3:$E$6</xm:f>
           </x14:formula1>
-          <xm:sqref>C22</xm:sqref>
+          <xm:sqref>C23</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1323,16 +1290,16 @@
   <sheetData>
     <row r="1" spans="1:7" customFormat="false">
       <c r="A1" s="5" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:7" customFormat="false">
@@ -1343,79 +1310,79 @@
     </row>
     <row r="3" spans="1:7" customFormat="false">
       <c r="A3" s="16" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E3" s="18" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G3" s="19" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:7" customFormat="false">
       <c r="A4" s="16" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E4" s="18" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="G4" s="19" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="5:7" customFormat="false">
       <c r="E5" s="18" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G5" s="19"/>
     </row>
     <row r="6" spans="5:7" customFormat="false">
       <c r="E6" s="18" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G6" s="19"/>
     </row>
     <row r="7" spans="5:7" customFormat="false">
       <c r="E7" s="18" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G7" s="19"/>
     </row>
     <row r="8" spans="1:7" customFormat="false">
       <c r="A8" s="33" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="G8" s="19"/>
     </row>
     <row r="9" spans="1:1" customFormat="false">
       <c r="A9" s="34" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:1" customFormat="false">
       <c r="A10" s="34" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:1" customFormat="false">
       <c r="A11" s="34" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:1" customFormat="false">
       <c r="A12" s="34" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:1" customFormat="false">
       <c r="A13" s="34" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1425,26 +1392,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="490201e0-5a85-47c8-9b04-cabe816267bb">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="f6e03047-2042-4ca4-baaf-a98f46f1920e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010028A7266EFD44C1488D53268B28E34142" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="17fbaf25eb06b561da31ccef8e0fdf10">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="490201e0-5a85-47c8-9b04-cabe816267bb" xmlns:ns3="f6e03047-2042-4ca4-baaf-a98f46f1920e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a1dd9b11af4de033f41fe38d66f243be" ns2:_="" ns3:_="">
     <xsd:import namespace="490201e0-5a85-47c8-9b04-cabe816267bb"/>
@@ -1685,4 +1632,24 @@
     <xs:element name="TermId" type="xs:string"/>
   </xs:schema>
 </ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="490201e0-5a85-47c8-9b04-cabe816267bb">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="f6e03047-2042-4ca4-baaf-a98f46f1920e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>